--- a/output/pdf_financials_xlsx/EMPS.xlsx
+++ b/output/pdf_financials_xlsx/EMPS.xlsx
@@ -1906,7 +1906,7 @@
         <v>0.005523</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.005523</v>
       </c>
     </row>
     <row r="92">
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.550292</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.368427</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3275,7 +3275,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3651,7 +3655,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>3.550292</v>
       </c>

--- a/output/pdf_financials_xlsx/EMPS.xlsx
+++ b/output/pdf_financials_xlsx/EMPS.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006158</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.25107</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.112128</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.554787</v>
+        <v>-1.560945</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.825476</v>
+        <v>-3.076546</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.343581</v>
+        <v>-4.455709</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.554787</v>
+        <v>-1.560945</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.825476</v>
+        <v>-3.076546</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.343581</v>
+        <v>-4.455709</v>
       </c>
     </row>
     <row r="30">
@@ -2947,7 +2947,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4875,7 +4879,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4941,7 +4945,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
